--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488153_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488153_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.722</v>
+        <v>5.9239</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1126</v>
+        <v>6.2653</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3906</v>
+        <v>-0.3413</v>
       </c>
       <c r="G2" t="n">
         <v>2.1935</v>
@@ -610,13 +610,13 @@
         <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3042</v>
+        <v>-0.1023</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2189</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0853</v>
+        <v>-0.0361</v>
       </c>
       <c r="V2" t="n">
         <v>3.4621</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9063</v>
+        <v>5.0168</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8213</v>
+        <v>4.7349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0849</v>
+        <v>0.2819</v>
       </c>
       <c r="G3" t="n">
         <v>6.7261</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8585</v>
+        <v>-0.748</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0373</v>
+        <v>-0.1237</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8213</v>
+        <v>-0.6243</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8877</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1841</v>
+        <v>3.2522</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6487</v>
+        <v>4.8265</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5354</v>
+        <v>-1.5743</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4466</v>
+        <v>5.0917</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0041</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4425</v>
+        <v>4.559</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3611</v>
+        <v>5.8651</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0708</v>
+        <v>0.5153</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2903</v>
+        <v>5.3498</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0855</v>
+        <v>-0.7734</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0667</v>
+        <v>0.0174</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1522</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3681</v>
+        <v>0.0482</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4004</v>
+        <v>-0.1122</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0324</v>
+        <v>0.1604</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8894</v>
+        <v>-1.8877</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6294</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. QUESADA PONS</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9087</v>
+        <v>2.9199</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0878</v>
+        <v>1.5076</v>
       </c>
       <c r="F5" t="n">
-        <v>0.821</v>
+        <v>1.4123</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5539</v>
+        <v>5.4466</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8583</v>
+        <v>4.0041</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6956</v>
+        <v>1.4425</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6138</v>
+        <v>4.3611</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2239</v>
+        <v>4.0708</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3899</v>
+        <v>0.2903</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9402</v>
+        <v>1.0855</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3656</v>
+        <v>-0.0667</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3057</v>
+        <v>1.1522</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1853</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1455</v>
+        <v>0.1038</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4004</v>
+        <v>0.2593</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.1555</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3144</v>
+        <v>-1.8894</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>P. QUESADA PONS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5355</v>
+        <v>2.7928</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2821</v>
+        <v>1.8487</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7466</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>5.0917</v>
+        <v>3.5539</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.8583</v>
       </c>
       <c r="I6" t="n">
-        <v>4.559</v>
+        <v>2.6956</v>
       </c>
       <c r="J6" t="n">
-        <v>5.8651</v>
+        <v>2.6138</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5153</v>
+        <v>1.2239</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3498</v>
+        <v>1.3899</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7734</v>
+        <v>0.9402</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0174</v>
+        <v>-0.3656</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7907999999999999</v>
+        <v>1.3057</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6685</v>
+        <v>-0.2615</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6566</v>
+        <v>0.1614</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.012</v>
+        <v>-0.4228</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8877</v>
+        <v>-0.3144</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8877</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.409</v>
+        <v>1.5115</v>
       </c>
       <c r="E7" t="n">
-        <v>1.372</v>
+        <v>1.2107</v>
       </c>
       <c r="F7" t="n">
-        <v>0.037</v>
+        <v>0.3008</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6133999999999999</v>
+        <v>3.4498</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0871</v>
+        <v>0.6651</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7005</v>
+        <v>2.7847</v>
       </c>
       <c r="J7" t="n">
-        <v>0.819</v>
+        <v>2.7644</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0725</v>
+        <v>0.1718</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7465000000000001</v>
+        <v>2.5926</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2056</v>
+        <v>0.6855</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1596</v>
+        <v>0.4933</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.046</v>
+        <v>0.1922</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1836</v>
+        <v>0.1178</v>
       </c>
       <c r="T7" t="n">
-        <v>0.868</v>
+        <v>-0.0152</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3156</v>
+        <v>0.133</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9439</v>
+        <v>-0.9444</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9425</v>
+        <v>0.4526</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6663</v>
+        <v>0.6865</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2762</v>
+        <v>-0.2338</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4498</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6651</v>
+        <v>-0.0871</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7847</v>
+        <v>0.7005</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7644</v>
+        <v>0.819</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1718</v>
+        <v>0.0725</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5926</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6855</v>
+        <v>-0.2056</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4933</v>
+        <v>-0.1596</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1922</v>
+        <v>-0.046</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4512</v>
+        <v>0.2273</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5596</v>
+        <v>0.1825</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1084</v>
+        <v>0.0448</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9444</v>
+        <v>-0.9439</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1648</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.789</v>
+        <v>-2.3744</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6242</v>
+        <v>2.2796</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8985</v>
+        <v>1.5627</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6082</v>
+        <v>1.8053</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2903</v>
+        <v>-0.2427</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7822</v>
+        <v>0.1784</v>
       </c>
       <c r="K9" t="n">
-        <v>0.73</v>
+        <v>1.4426</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0522</v>
+        <v>-1.2643</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1163</v>
+        <v>1.3843</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1219</v>
+        <v>0.3627</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2381</v>
+        <v>1.0216</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1117</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6785</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0883</v>
+        <v>-0.3849</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7668</v>
+        <v>-0.2164</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.63</v>
+        <v>-0.315</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.63</v>
+        <v>-0.315</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5537</v>
+        <v>-0.3076</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3316</v>
+        <v>-1.6363</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8854</v>
+        <v>1.3287</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3879</v>
+        <v>0.8985</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0731</v>
+        <v>0.6082</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3148</v>
+        <v>0.2903</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2158</v>
+        <v>0.7822</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1329</v>
+        <v>0.73</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0829</v>
+        <v>0.0522</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6037</v>
+        <v>0.1163</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.206</v>
+        <v>-0.1219</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3977</v>
+        <v>0.2381</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q10" t="n">
+        <v>-1.8529</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.9264</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.09229999999999999</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.143</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.2589</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5669</v>
+        <v>-0.4804</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6249</v>
+        <v>1.4296</v>
       </c>
       <c r="F11" t="n">
-        <v>2.058</v>
+        <v>-1.91</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5627</v>
+        <v>-1.3879</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8053</v>
+        <v>-0.0731</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2427</v>
+        <v>-1.3148</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1784</v>
+        <v>0.2158</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4426</v>
+        <v>0.1329</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2643</v>
+        <v>0.0829</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3843</v>
+        <v>-1.6037</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3627</v>
+        <v>-0.206</v>
       </c>
       <c r="O11" t="n">
-        <v>1.0216</v>
+        <v>-1.3977</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0734</v>
+        <v>-0.019</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6354</v>
+        <v>-0.0451</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.438</v>
+        <v>0.0261</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.315</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8056</v>
+        <v>-0.677</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1059</v>
+        <v>-1.0512</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3003</v>
+        <v>0.3742</v>
       </c>
       <c r="G12" t="n">
         <v>3.1975</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6123</v>
+        <v>-0.4838</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0373</v>
+        <v>0.0174</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.575</v>
+        <v>-0.5012</v>
       </c>
       <c r="V12" t="n">
         <v>0.315</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1934</v>
+        <v>-1.4391</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0999</v>
+        <v>0.002</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2933</v>
+        <v>-1.4411</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7851</v>
@@ -1468,13 +1468,13 @@
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7944</v>
+        <v>0.5487</v>
       </c>
       <c r="T13" t="n">
-        <v>0.291</v>
+        <v>0.1931</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5034</v>
+        <v>0.3556</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3144</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.3237</v>
+        <v>18.8709</v>
       </c>
       <c r="E14" t="n">
-        <v>16.9025</v>
+        <v>17.4499</v>
       </c>
       <c r="F14" t="n">
         <v>1.4211</v>
@@ -1534,7 +1534,7 @@
         <v>-1.5086</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1519999999999999</v>
+        <v>-0.1519999999999995</v>
       </c>
       <c r="P14" t="n">
         <v>-3.7056</v>
@@ -1546,16 +1546,16 @@
         <v>12.9699</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1813</v>
+        <v>-0.6345000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4166</v>
+        <v>0.1307999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7650000000000002</v>
+        <v>-0.7650999999999998</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.3498</v>
+        <v>-5.349799999999999</v>
       </c>
       <c r="W14" t="n">
         <v>3.7737</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5791</v>
+        <v>3.3047</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5636</v>
+        <v>5.1512</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9846</v>
+        <v>-1.8465</v>
       </c>
       <c r="G15" t="n">
         <v>-1.8749</v>
@@ -1624,13 +1624,13 @@
         <v>3.1499</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3221</v>
+        <v>0.4035</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.618</v>
+        <v>-0.0304</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2959</v>
+        <v>0.434</v>
       </c>
       <c r="V15" t="n">
         <v>4.4054</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2021</v>
+        <v>1.5797</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7881</v>
+        <v>3.831</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5861</v>
+        <v>-2.2513</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7907</v>
+        <v>-1.2871</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7068</v>
+        <v>-1.9092</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4975</v>
+        <v>0.6221</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9684</v>
+        <v>3.7534</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7611</v>
+        <v>-0.1248</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2074</v>
+        <v>3.8782</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.7591</v>
+        <v>-5.0405</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0543</v>
+        <v>-1.7844</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7048</v>
+        <v>-3.2561</v>
       </c>
       <c r="P16" t="n">
+        <v>2.7793</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.9264</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.9264</v>
+        <v>2.7793</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6778</v>
+        <v>-0.2269</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7461</v>
+        <v>-0.2369</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9316</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="W16" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.315</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.6942</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6351</v>
+        <v>2.4944</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7586</v>
+        <v>-1.8002</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2871</v>
+        <v>-0.7907</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9092</v>
+        <v>0.7068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6221</v>
+        <v>-1.4975</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7534</v>
+        <v>2.9684</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1248</v>
+        <v>2.7611</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8782</v>
+        <v>0.2074</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.0405</v>
+        <v>-3.7591</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7844</v>
+        <v>-2.0543</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.2561</v>
+        <v>-1.7048</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
+        <v>-0.9264</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.1699</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="W17" t="n">
         <v>0</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.7793</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.9302</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.4327</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.4974</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.3144</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.3144</v>
-      </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3052</v>
+        <v>-0.0355</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7114</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4062</v>
+        <v>0.4801</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4503</v>
@@ -1858,13 +1858,13 @@
         <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3002</v>
+        <v>-0.0305</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.143</v>
+        <v>0.0529</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1572</v>
+        <v>-0.0833</v>
       </c>
       <c r="V18" t="n">
         <v>1.26</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.5233</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2297</v>
+        <v>-1.3277</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3955</v>
+        <v>0.8044</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8123</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6339</v>
+        <v>-0.323</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1467</v>
+        <v>-0.2446</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4872</v>
+        <v>-0.0784</v>
       </c>
       <c r="V19" t="n">
         <v>0.315</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6379</v>
+        <v>-3.5314</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3874</v>
+        <v>-1.4853</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2506</v>
+        <v>-2.0461</v>
       </c>
       <c r="G20" t="n">
         <v>-4.1258</v>
@@ -2014,13 +2014,13 @@
         <v>2.4087</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2644</v>
+        <v>0.3709</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4514</v>
+        <v>0.3535</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.187</v>
+        <v>0.0174</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2589</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7402</v>
+        <v>-3.8146</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.453</v>
+        <v>-2.3551</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2872</v>
+        <v>-1.4595</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3311</v>
@@ -2092,13 +2092,13 @@
         <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5168</v>
+        <v>0.4424</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0721</v>
+        <v>0.1701</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4447</v>
+        <v>0.2723</v>
       </c>
       <c r="V21" t="n">
         <v>0.63</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3199</v>
+        <v>-5.8468</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8309</v>
+        <v>-2.4392</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4889</v>
+        <v>-3.4076</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4539</v>
@@ -2170,13 +2170,13 @@
         <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5128</v>
+        <v>-0.0398</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6143</v>
+        <v>-0.2226</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1015</v>
+        <v>0.1828</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.1439</v>
+        <v>-8.844900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7954</v>
+        <v>-4.7747</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3484</v>
+        <v>-4.0701</v>
       </c>
       <c r="G23" t="n">
         <v>-10.4347</v>
@@ -2248,13 +2248,13 @@
         <v>2.4087</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4216</v>
+        <v>0.7206</v>
       </c>
       <c r="T23" t="n">
-        <v>1.45</v>
+        <v>0.4707</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0284</v>
+        <v>0.2499</v>
       </c>
       <c r="V23" t="n">
         <v>0.3133</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.3236</v>
+        <v>-17.0179</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.420999999999998</v>
+        <v>-1.421</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.9027</v>
+        <v>-15.5968</v>
       </c>
       <c r="G24" t="n">
         <v>-28.5608</v>
@@ -2302,7 +2302,7 @@
         <v>1.6603</v>
       </c>
       <c r="K24" t="n">
-        <v>1.508299999999999</v>
+        <v>1.5083</v>
       </c>
       <c r="L24" t="n">
         <v>0.1520999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>16.6757</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1814</v>
+        <v>2.4871</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7648999999999999</v>
+        <v>0.7651000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4165</v>
+        <v>1.7221</v>
       </c>
       <c r="V24" t="n">
         <v>5.3498</v>
